--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/MAINE_2016.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/MAINE_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C6">
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -524,7 +559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -560,7 +600,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C14">
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -622,7 +672,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C18">
@@ -633,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -646,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -677,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C22">
@@ -690,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Total</t>
@@ -721,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -752,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -783,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -814,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -827,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -840,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -853,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C34">
@@ -866,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -897,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -928,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Total</t>
@@ -959,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C41">
@@ -972,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -985,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Paso del Macho</t>
+          <t>Paso Del Macho</t>
         </is>
       </c>
       <c r="C43">
@@ -998,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Soteapan</t>
@@ -1011,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1034,76 +1179,6 @@
       </c>
       <c r="D46">
         <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
